--- a/src_data/df_zs10a_ls.xlsx
+++ b/src_data/df_zs10a_ls.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="550">
   <si>
     <t>doc_id</t>
   </si>
@@ -17610,6 +17610,12 @@
     <t>2010-12-16</t>
   </si>
   <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -18440,7 +18446,7 @@
     <t>10.5281/zenodo.3942742</t>
   </si>
   <si>
-    <t>10.5281/zenodo.12814022</t>
+    <t>10.5281/zenodo.15153244</t>
   </si>
   <si>
     <t>Creative Commons Zero 1.0 Universal</t>
@@ -18950,26 +18956,26 @@
       <c r="F2" t="s">
         <v>250</v>
       </c>
-      <c r="G2">
-        <v>2009</v>
+      <c r="G2" t="s">
+        <v>296</v>
       </c>
       <c r="H2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N2">
         <v>24</v>
@@ -18981,25 +18987,25 @@
         <v>2007</v>
       </c>
       <c r="R2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="V2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Y2">
         <v>0</v>
@@ -19029,16 +19035,16 @@
         <v>142</v>
       </c>
       <c r="AH2" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -19060,26 +19066,26 @@
       <c r="F3" t="s">
         <v>251</v>
       </c>
-      <c r="G3">
-        <v>2009</v>
+      <c r="G3" t="s">
+        <v>296</v>
       </c>
       <c r="H3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N3">
         <v>116</v>
@@ -19091,25 +19097,25 @@
         <v>2007</v>
       </c>
       <c r="R3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="U3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="V3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Y3">
         <v>0</v>
@@ -19139,16 +19145,16 @@
         <v>149</v>
       </c>
       <c r="AH3" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -19170,26 +19176,26 @@
       <c r="F4" t="s">
         <v>252</v>
       </c>
-      <c r="G4">
-        <v>2009</v>
+      <c r="G4" t="s">
+        <v>296</v>
       </c>
       <c r="H4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N4">
         <v>197</v>
@@ -19204,19 +19210,19 @@
         <v>0</v>
       </c>
       <c r="T4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="U4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="V4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W4" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X4" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y4">
         <v>0</v>
@@ -19246,16 +19252,16 @@
         <v>73</v>
       </c>
       <c r="AH4" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK4" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -19277,26 +19283,26 @@
       <c r="F5" t="s">
         <v>253</v>
       </c>
-      <c r="G5">
-        <v>2009</v>
+      <c r="G5" t="s">
+        <v>296</v>
       </c>
       <c r="H5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N5">
         <v>141</v>
@@ -19311,19 +19317,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="U5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="V5" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W5" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X5" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Y5">
         <v>0</v>
@@ -19353,16 +19359,16 @@
         <v>139</v>
       </c>
       <c r="AH5" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI5" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ5" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK5" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -19384,26 +19390,26 @@
       <c r="F6" t="s">
         <v>254</v>
       </c>
-      <c r="G6">
-        <v>2009</v>
+      <c r="G6" t="s">
+        <v>296</v>
       </c>
       <c r="H6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N6">
         <v>158</v>
@@ -19415,25 +19421,25 @@
         <v>2004</v>
       </c>
       <c r="R6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="U6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="V6" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W6" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X6" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Y6">
         <v>0</v>
@@ -19463,16 +19469,16 @@
         <v>158</v>
       </c>
       <c r="AH6" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI6" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -19494,26 +19500,26 @@
       <c r="F7" t="s">
         <v>254</v>
       </c>
-      <c r="G7">
-        <v>2009</v>
+      <c r="G7" t="s">
+        <v>296</v>
       </c>
       <c r="H7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J7" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N7">
         <v>86</v>
@@ -19525,25 +19531,25 @@
         <v>2006</v>
       </c>
       <c r="R7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="U7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="V7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X7" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Y7">
         <v>0</v>
@@ -19573,16 +19579,16 @@
         <v>109</v>
       </c>
       <c r="AH7" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI7" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ7" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK7" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -19604,26 +19610,26 @@
       <c r="F8" t="s">
         <v>255</v>
       </c>
-      <c r="G8">
-        <v>2009</v>
+      <c r="G8" t="s">
+        <v>296</v>
       </c>
       <c r="H8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I8" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J8" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K8" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L8" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M8" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N8">
         <v>14</v>
@@ -19635,25 +19641,25 @@
         <v>2007</v>
       </c>
       <c r="R8" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="U8" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="V8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W8" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X8" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Y8">
         <v>0</v>
@@ -19683,16 +19689,16 @@
         <v>190</v>
       </c>
       <c r="AH8" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI8" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ8" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK8" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -19714,26 +19720,26 @@
       <c r="F9" t="s">
         <v>256</v>
       </c>
-      <c r="G9">
-        <v>2009</v>
+      <c r="G9" t="s">
+        <v>296</v>
       </c>
       <c r="H9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N9">
         <v>156</v>
@@ -19745,25 +19751,25 @@
         <v>2004</v>
       </c>
       <c r="R9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="U9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="V9" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W9" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X9" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Y9">
         <v>0</v>
@@ -19793,16 +19799,16 @@
         <v>232</v>
       </c>
       <c r="AH9" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI9" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ9" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK9" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -19824,26 +19830,26 @@
       <c r="F10" t="s">
         <v>256</v>
       </c>
-      <c r="G10">
-        <v>2009</v>
+      <c r="G10" t="s">
+        <v>296</v>
       </c>
       <c r="H10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J10" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N10">
         <v>56</v>
@@ -19855,25 +19861,25 @@
         <v>2005</v>
       </c>
       <c r="R10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="U10" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="V10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W10" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X10" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Y10">
         <v>0</v>
@@ -19903,16 +19909,16 @@
         <v>272</v>
       </c>
       <c r="AH10" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI10" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ10" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK10" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -19934,26 +19940,26 @@
       <c r="F11" t="s">
         <v>256</v>
       </c>
-      <c r="G11">
-        <v>2009</v>
+      <c r="G11" t="s">
+        <v>296</v>
       </c>
       <c r="H11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N11">
         <v>78</v>
@@ -19968,19 +19974,19 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="U11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="V11" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X11" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Y11">
         <v>0</v>
@@ -20010,16 +20016,16 @@
         <v>144</v>
       </c>
       <c r="AH11" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI11" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -20041,26 +20047,26 @@
       <c r="F12" t="s">
         <v>256</v>
       </c>
-      <c r="G12">
-        <v>2009</v>
+      <c r="G12" t="s">
+        <v>296</v>
       </c>
       <c r="H12" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I12" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L12" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M12" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N12">
         <v>92</v>
@@ -20072,25 +20078,25 @@
         <v>2005</v>
       </c>
       <c r="R12" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="U12" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="V12" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W12" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X12" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Y12">
         <v>0</v>
@@ -20120,16 +20126,16 @@
         <v>130</v>
       </c>
       <c r="AH12" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI12" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ12" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK12" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -20151,26 +20157,26 @@
       <c r="F13" t="s">
         <v>257</v>
       </c>
-      <c r="G13">
-        <v>2009</v>
+      <c r="G13" t="s">
+        <v>296</v>
       </c>
       <c r="H13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I13" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L13" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M13" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N13">
         <v>148</v>
@@ -20182,25 +20188,25 @@
         <v>2005</v>
       </c>
       <c r="R13" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="U13" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="V13" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W13" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X13" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="Y13">
         <v>0</v>
@@ -20230,16 +20236,16 @@
         <v>140</v>
       </c>
       <c r="AH13" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI13" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ13" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK13" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -20261,26 +20267,26 @@
       <c r="F14" t="s">
         <v>258</v>
       </c>
-      <c r="G14">
-        <v>2009</v>
+      <c r="G14" t="s">
+        <v>296</v>
       </c>
       <c r="H14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J14" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K14" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L14" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N14">
         <v>113</v>
@@ -20295,19 +20301,19 @@
         <v>0</v>
       </c>
       <c r="T14" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="U14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="V14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W14" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X14" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="Y14">
         <v>0</v>
@@ -20337,16 +20343,16 @@
         <v>125</v>
       </c>
       <c r="AH14" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI14" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ14" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK14" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -20368,26 +20374,26 @@
       <c r="F15" t="s">
         <v>258</v>
       </c>
-      <c r="G15">
-        <v>2009</v>
+      <c r="G15" t="s">
+        <v>296</v>
       </c>
       <c r="H15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K15" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N15">
         <v>140</v>
@@ -20399,25 +20405,25 @@
         <v>2005</v>
       </c>
       <c r="R15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="U15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="V15" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W15" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X15" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Y15">
         <v>0</v>
@@ -20447,16 +20453,16 @@
         <v>126</v>
       </c>
       <c r="AH15" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI15" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ15" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK15" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -20478,26 +20484,26 @@
       <c r="F16" t="s">
         <v>258</v>
       </c>
-      <c r="G16">
-        <v>2009</v>
+      <c r="G16" t="s">
+        <v>296</v>
       </c>
       <c r="H16" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I16" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J16" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K16" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L16" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N16">
         <v>9</v>
@@ -20512,19 +20518,19 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="U16" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="V16" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W16" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X16" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Y16">
         <v>0</v>
@@ -20554,16 +20560,16 @@
         <v>81</v>
       </c>
       <c r="AH16" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI16" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ16" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK16" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -20585,26 +20591,26 @@
       <c r="F17" t="s">
         <v>259</v>
       </c>
-      <c r="G17">
-        <v>2009</v>
+      <c r="G17" t="s">
+        <v>296</v>
       </c>
       <c r="H17" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I17" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J17" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K17" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M17" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N17">
         <v>99</v>
@@ -20619,19 +20625,19 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="U17" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="V17" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W17" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X17" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Y17">
         <v>0</v>
@@ -20661,16 +20667,16 @@
         <v>131</v>
       </c>
       <c r="AH17" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI17" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ17" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK17" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -20692,26 +20698,26 @@
       <c r="F18" t="s">
         <v>260</v>
       </c>
-      <c r="G18">
-        <v>2009</v>
+      <c r="G18" t="s">
+        <v>296</v>
       </c>
       <c r="H18" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I18" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J18" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K18" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L18" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M18" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N18">
         <v>138</v>
@@ -20723,25 +20729,25 @@
         <v>2005</v>
       </c>
       <c r="R18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="U18" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="V18" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W18" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="X18" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="Y18">
         <v>0</v>
@@ -20771,16 +20777,16 @@
         <v>167</v>
       </c>
       <c r="AH18" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI18" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ18" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK18" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -20802,26 +20808,26 @@
       <c r="F19" t="s">
         <v>261</v>
       </c>
-      <c r="G19">
-        <v>2009</v>
+      <c r="G19" t="s">
+        <v>296</v>
       </c>
       <c r="H19" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I19" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K19" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L19" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M19" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N19">
         <v>19</v>
@@ -20836,19 +20842,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U19" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="V19" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W19" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X19" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y19">
         <v>0</v>
@@ -20878,16 +20884,16 @@
         <v>425</v>
       </c>
       <c r="AH19" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI19" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ19" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK19" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -20909,26 +20915,26 @@
       <c r="F20" t="s">
         <v>261</v>
       </c>
-      <c r="G20">
-        <v>2009</v>
+      <c r="G20" t="s">
+        <v>296</v>
       </c>
       <c r="H20" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I20" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J20" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K20" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M20" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N20">
         <v>19</v>
@@ -20943,19 +20949,19 @@
         <v>1</v>
       </c>
       <c r="T20" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="U20" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="V20" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W20" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X20" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="Y20">
         <v>0</v>
@@ -20985,16 +20991,16 @@
         <v>20</v>
       </c>
       <c r="AH20" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI20" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ20" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK20" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -21016,26 +21022,26 @@
       <c r="F21" t="s">
         <v>262</v>
       </c>
-      <c r="G21">
-        <v>2009</v>
+      <c r="G21" t="s">
+        <v>296</v>
       </c>
       <c r="H21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I21" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J21" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K21" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M21" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N21">
         <v>167</v>
@@ -21050,19 +21056,19 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="U21" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="V21" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W21" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X21" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y21">
         <v>0</v>
@@ -21092,16 +21098,16 @@
         <v>94</v>
       </c>
       <c r="AH21" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI21" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ21" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK21" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -21123,26 +21129,26 @@
       <c r="F22" t="s">
         <v>262</v>
       </c>
-      <c r="G22">
-        <v>2009</v>
+      <c r="G22" t="s">
+        <v>296</v>
       </c>
       <c r="H22" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I22" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J22" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K22" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L22" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M22" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N22">
         <v>28</v>
@@ -21154,25 +21160,25 @@
         <v>2008</v>
       </c>
       <c r="R22" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="U22" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="V22" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W22" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X22" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Y22">
         <v>0</v>
@@ -21202,16 +21208,16 @@
         <v>94</v>
       </c>
       <c r="AH22" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI22" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ22" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK22" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -21233,26 +21239,26 @@
       <c r="F23" t="s">
         <v>262</v>
       </c>
-      <c r="G23">
-        <v>2009</v>
+      <c r="G23" t="s">
+        <v>296</v>
       </c>
       <c r="H23" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J23" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L23" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M23" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N23">
         <v>22</v>
@@ -21264,25 +21270,25 @@
         <v>2006</v>
       </c>
       <c r="R23" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="U23" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="V23" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W23" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X23" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="Y23">
         <v>0</v>
@@ -21312,16 +21318,16 @@
         <v>159</v>
       </c>
       <c r="AH23" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI23" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ23" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK23" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -21343,26 +21349,26 @@
       <c r="F24" t="s">
         <v>263</v>
       </c>
-      <c r="G24">
-        <v>2009</v>
+      <c r="G24" t="s">
+        <v>296</v>
       </c>
       <c r="H24" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I24" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J24" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K24" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L24" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N24">
         <v>18</v>
@@ -21374,25 +21380,25 @@
         <v>2008</v>
       </c>
       <c r="R24" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="U24" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="V24" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W24" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X24" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="Y24">
         <v>0</v>
@@ -21422,16 +21428,16 @@
         <v>215</v>
       </c>
       <c r="AH24" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI24" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ24" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK24" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -21453,26 +21459,26 @@
       <c r="F25" t="s">
         <v>264</v>
       </c>
-      <c r="G25">
-        <v>2009</v>
+      <c r="G25" t="s">
+        <v>296</v>
       </c>
       <c r="H25" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I25" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J25" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L25" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M25" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N25">
         <v>2</v>
@@ -21484,25 +21490,25 @@
         <v>2008</v>
       </c>
       <c r="R25" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="U25" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="V25" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W25" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X25" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Y25">
         <v>0</v>
@@ -21532,16 +21538,16 @@
         <v>279</v>
       </c>
       <c r="AH25" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI25" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ25" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK25" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -21563,26 +21569,26 @@
       <c r="F26" t="s">
         <v>264</v>
       </c>
-      <c r="G26">
-        <v>2009</v>
+      <c r="G26" t="s">
+        <v>296</v>
       </c>
       <c r="H26" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I26" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J26" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K26" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L26" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M26" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N26">
         <v>40</v>
@@ -21597,19 +21603,19 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="U26" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="V26" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W26" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X26" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Y26">
         <v>0</v>
@@ -21639,16 +21645,16 @@
         <v>103</v>
       </c>
       <c r="AH26" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI26" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ26" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK26" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -21670,26 +21676,26 @@
       <c r="F27" t="s">
         <v>265</v>
       </c>
-      <c r="G27">
-        <v>2009</v>
+      <c r="G27" t="s">
+        <v>296</v>
       </c>
       <c r="H27" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I27" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J27" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K27" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L27" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M27" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N27">
         <v>36</v>
@@ -21701,25 +21707,25 @@
         <v>2008</v>
       </c>
       <c r="R27" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="U27" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="V27" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W27" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X27" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Y27">
         <v>0</v>
@@ -21749,16 +21755,16 @@
         <v>91</v>
       </c>
       <c r="AH27" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI27" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ27" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK27" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -21780,26 +21786,26 @@
       <c r="F28" t="s">
         <v>266</v>
       </c>
-      <c r="G28">
-        <v>2009</v>
+      <c r="G28" t="s">
+        <v>296</v>
       </c>
       <c r="H28" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I28" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J28" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K28" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L28" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N28">
         <v>8</v>
@@ -21814,19 +21820,19 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="U28" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="V28" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W28" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X28" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Y28">
         <v>0</v>
@@ -21856,16 +21862,16 @@
         <v>141</v>
       </c>
       <c r="AH28" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI28" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ28" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK28" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -21887,26 +21893,26 @@
       <c r="F29" t="s">
         <v>267</v>
       </c>
-      <c r="G29">
-        <v>2009</v>
+      <c r="G29" t="s">
+        <v>296</v>
       </c>
       <c r="H29" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I29" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J29" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K29" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L29" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M29" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N29">
         <v>76</v>
@@ -21921,19 +21927,19 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="U29" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="V29" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W29" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X29" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y29">
         <v>0</v>
@@ -21963,16 +21969,16 @@
         <v>158</v>
       </c>
       <c r="AH29" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI29" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ29" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK29" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -21994,26 +22000,26 @@
       <c r="F30" t="s">
         <v>268</v>
       </c>
-      <c r="G30">
-        <v>2009</v>
+      <c r="G30" t="s">
+        <v>296</v>
       </c>
       <c r="H30" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I30" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J30" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K30" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L30" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N30">
         <v>132</v>
@@ -22028,19 +22034,19 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="U30" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="V30" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W30" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X30" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y30">
         <v>0</v>
@@ -22070,16 +22076,16 @@
         <v>194</v>
       </c>
       <c r="AH30" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI30" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ30" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK30" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -22101,26 +22107,26 @@
       <c r="F31" t="s">
         <v>269</v>
       </c>
-      <c r="G31">
-        <v>2009</v>
+      <c r="G31" t="s">
+        <v>296</v>
       </c>
       <c r="H31" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I31" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J31" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K31" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L31" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N31">
         <v>61</v>
@@ -22135,19 +22141,19 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="U31" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="V31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X31" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y31">
         <v>0</v>
@@ -22177,16 +22183,16 @@
         <v>305</v>
       </c>
       <c r="AH31" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -22208,26 +22214,26 @@
       <c r="F32" t="s">
         <v>270</v>
       </c>
-      <c r="G32">
-        <v>2009</v>
+      <c r="G32" t="s">
+        <v>296</v>
       </c>
       <c r="H32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I32" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J32" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K32" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L32" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N32">
         <v>38</v>
@@ -22239,25 +22245,25 @@
         <v>2008</v>
       </c>
       <c r="R32" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="U32" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="V32" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W32" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X32" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Y32">
         <v>0</v>
@@ -22287,16 +22293,16 @@
         <v>128</v>
       </c>
       <c r="AH32" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI32" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ32" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK32" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -22318,26 +22324,26 @@
       <c r="F33" t="s">
         <v>270</v>
       </c>
-      <c r="G33">
-        <v>2009</v>
+      <c r="G33" t="s">
+        <v>296</v>
       </c>
       <c r="H33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I33" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J33" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K33" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L33" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N33">
         <v>58</v>
@@ -22349,25 +22355,25 @@
         <v>2007</v>
       </c>
       <c r="R33" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="U33" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="V33" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W33" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X33" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="Y33">
         <v>0</v>
@@ -22397,16 +22403,16 @@
         <v>431</v>
       </c>
       <c r="AH33" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI33" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK33" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -22428,26 +22434,26 @@
       <c r="F34" t="s">
         <v>270</v>
       </c>
-      <c r="G34">
-        <v>2009</v>
+      <c r="G34" t="s">
+        <v>296</v>
       </c>
       <c r="H34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J34" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K34" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L34" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N34">
         <v>6</v>
@@ -22462,19 +22468,19 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="U34" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="V34" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W34" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X34" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y34">
         <v>0</v>
@@ -22504,16 +22510,16 @@
         <v>84</v>
       </c>
       <c r="AH34" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI34" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ34" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK34" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -22535,26 +22541,26 @@
       <c r="F35" t="s">
         <v>271</v>
       </c>
-      <c r="G35">
-        <v>2010</v>
+      <c r="G35" t="s">
+        <v>297</v>
       </c>
       <c r="H35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K35" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L35" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N35">
         <v>175</v>
@@ -22569,19 +22575,19 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="U35" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="V35" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W35" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X35" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y35">
         <v>0</v>
@@ -22611,16 +22617,16 @@
         <v>161</v>
       </c>
       <c r="AH35" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI35" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ35" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK35" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -22642,26 +22648,26 @@
       <c r="F36" t="s">
         <v>272</v>
       </c>
-      <c r="G36">
-        <v>2010</v>
+      <c r="G36" t="s">
+        <v>297</v>
       </c>
       <c r="H36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L36" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N36">
         <v>37</v>
@@ -22676,19 +22682,19 @@
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="U36" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="V36" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W36" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X36" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="Y36">
         <v>0</v>
@@ -22718,16 +22724,16 @@
         <v>119</v>
       </c>
       <c r="AH36" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI36" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ36" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK36" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -22749,26 +22755,26 @@
       <c r="F37" t="s">
         <v>273</v>
       </c>
-      <c r="G37">
-        <v>2010</v>
+      <c r="G37" t="s">
+        <v>297</v>
       </c>
       <c r="H37" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L37" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M37" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N37">
         <v>36</v>
@@ -22780,25 +22786,25 @@
         <v>2008</v>
       </c>
       <c r="R37" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="S37">
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="U37" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="V37" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W37" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X37" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Y37">
         <v>0</v>
@@ -22828,16 +22834,16 @@
         <v>203</v>
       </c>
       <c r="AH37" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI37" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ37" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK37" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="38" spans="1:37">
@@ -22859,26 +22865,26 @@
       <c r="F38" t="s">
         <v>273</v>
       </c>
-      <c r="G38">
-        <v>2010</v>
+      <c r="G38" t="s">
+        <v>297</v>
       </c>
       <c r="H38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I38" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N38">
         <v>4</v>
@@ -22890,25 +22896,25 @@
         <v>2007</v>
       </c>
       <c r="R38" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="U38" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="V38" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W38" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X38" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Y38">
         <v>0</v>
@@ -22938,16 +22944,16 @@
         <v>199</v>
       </c>
       <c r="AH38" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI38" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ38" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK38" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="39" spans="1:37">
@@ -22969,26 +22975,26 @@
       <c r="F39" t="s">
         <v>274</v>
       </c>
-      <c r="G39">
-        <v>2010</v>
+      <c r="G39" t="s">
+        <v>297</v>
       </c>
       <c r="H39" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N39">
         <v>14</v>
@@ -23003,19 +23009,19 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U39" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="V39" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W39" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X39" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y39">
         <v>0</v>
@@ -23045,16 +23051,16 @@
         <v>142</v>
       </c>
       <c r="AH39" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI39" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ39" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK39" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="40" spans="1:37">
@@ -23076,26 +23082,26 @@
       <c r="F40" t="s">
         <v>274</v>
       </c>
-      <c r="G40">
-        <v>2010</v>
+      <c r="G40" t="s">
+        <v>297</v>
       </c>
       <c r="H40" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I40" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J40" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K40" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N40">
         <v>14</v>
@@ -23110,19 +23116,19 @@
         <v>1</v>
       </c>
       <c r="T40" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="U40" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="V40" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W40" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X40" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="Y40">
         <v>0</v>
@@ -23152,16 +23158,16 @@
         <v>6</v>
       </c>
       <c r="AH40" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI40" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ40" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK40" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="41" spans="1:37">
@@ -23183,26 +23189,26 @@
       <c r="F41" t="s">
         <v>274</v>
       </c>
-      <c r="G41">
-        <v>2010</v>
+      <c r="G41" t="s">
+        <v>297</v>
       </c>
       <c r="H41" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I41" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J41" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N41">
         <v>52</v>
@@ -23214,25 +23220,25 @@
         <v>2008</v>
       </c>
       <c r="R41" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S41">
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="U41" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="V41" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W41" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X41" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Y41">
         <v>0</v>
@@ -23262,16 +23268,16 @@
         <v>146</v>
       </c>
       <c r="AH41" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI41" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ41" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK41" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="42" spans="1:37">
@@ -23293,26 +23299,26 @@
       <c r="F42" t="s">
         <v>274</v>
       </c>
-      <c r="G42">
-        <v>2010</v>
+      <c r="G42" t="s">
+        <v>297</v>
       </c>
       <c r="H42" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I42" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J42" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K42" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L42" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N42">
         <v>95</v>
@@ -23327,19 +23333,19 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="U42" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="V42" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W42" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X42" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Y42">
         <v>0</v>
@@ -23369,16 +23375,16 @@
         <v>110</v>
       </c>
       <c r="AH42" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI42" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ42" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK42" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="43" spans="1:37">
@@ -23400,26 +23406,26 @@
       <c r="F43" t="s">
         <v>275</v>
       </c>
-      <c r="G43">
-        <v>2010</v>
+      <c r="G43" t="s">
+        <v>297</v>
       </c>
       <c r="H43" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I43" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J43" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K43" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L43" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N43">
         <v>100</v>
@@ -23431,25 +23437,25 @@
         <v>2005</v>
       </c>
       <c r="R43" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="U43" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="V43" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W43" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X43" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="Y43">
         <v>0</v>
@@ -23479,16 +23485,16 @@
         <v>269</v>
       </c>
       <c r="AH43" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI43" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ43" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK43" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="44" spans="1:37">
@@ -23510,26 +23516,26 @@
       <c r="F44" t="s">
         <v>276</v>
       </c>
-      <c r="G44">
-        <v>2010</v>
+      <c r="G44" t="s">
+        <v>297</v>
       </c>
       <c r="H44" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I44" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J44" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K44" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L44" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N44">
         <v>54</v>
@@ -23541,25 +23547,25 @@
         <v>2006</v>
       </c>
       <c r="R44" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="S44">
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="U44" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="V44" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W44" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X44" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Y44">
         <v>0</v>
@@ -23589,16 +23595,16 @@
         <v>188</v>
       </c>
       <c r="AH44" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI44" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ44" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK44" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="45" spans="1:37">
@@ -23620,26 +23626,26 @@
       <c r="F45" t="s">
         <v>276</v>
       </c>
-      <c r="G45">
-        <v>2010</v>
+      <c r="G45" t="s">
+        <v>297</v>
       </c>
       <c r="H45" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I45" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J45" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K45" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L45" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M45" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N45">
         <v>74</v>
@@ -23651,25 +23657,25 @@
         <v>2009</v>
       </c>
       <c r="R45" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="S45">
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="U45" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="V45" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W45" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X45" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="Y45">
         <v>0</v>
@@ -23699,16 +23705,16 @@
         <v>143</v>
       </c>
       <c r="AH45" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI45" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ45" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK45" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="46" spans="1:37">
@@ -23730,26 +23736,26 @@
       <c r="F46" t="s">
         <v>277</v>
       </c>
-      <c r="G46">
-        <v>2010</v>
+      <c r="G46" t="s">
+        <v>297</v>
       </c>
       <c r="H46" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I46" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J46" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K46" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L46" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N46">
         <v>96</v>
@@ -23764,19 +23770,19 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="U46" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="V46" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W46" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X46" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Y46">
         <v>0</v>
@@ -23806,16 +23812,16 @@
         <v>163</v>
       </c>
       <c r="AH46" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI46" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ46" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK46" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="47" spans="1:37">
@@ -23837,26 +23843,26 @@
       <c r="F47" t="s">
         <v>278</v>
       </c>
-      <c r="G47">
-        <v>2010</v>
+      <c r="G47" t="s">
+        <v>297</v>
       </c>
       <c r="H47" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I47" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J47" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K47" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L47" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M47" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N47">
         <v>10</v>
@@ -23868,25 +23874,25 @@
         <v>2009</v>
       </c>
       <c r="R47" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="U47" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="V47" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W47" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X47" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Y47">
         <v>0</v>
@@ -23916,16 +23922,16 @@
         <v>132</v>
       </c>
       <c r="AH47" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI47" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ47" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK47" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="48" spans="1:37">
@@ -23947,26 +23953,26 @@
       <c r="F48" t="s">
         <v>278</v>
       </c>
-      <c r="G48">
-        <v>2010</v>
+      <c r="G48" t="s">
+        <v>297</v>
       </c>
       <c r="H48" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I48" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J48" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K48" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L48" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M48" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N48">
         <v>28</v>
@@ -23978,25 +23984,25 @@
         <v>2008</v>
       </c>
       <c r="R48" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="S48">
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="U48" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="V48" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W48" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X48" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="Y48">
         <v>0</v>
@@ -24026,16 +24032,16 @@
         <v>320</v>
       </c>
       <c r="AH48" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI48" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ48" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK48" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="49" spans="1:37">
@@ -24057,26 +24063,26 @@
       <c r="F49" t="s">
         <v>278</v>
       </c>
-      <c r="G49">
-        <v>2010</v>
+      <c r="G49" t="s">
+        <v>297</v>
       </c>
       <c r="H49" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I49" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J49" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K49" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L49" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M49" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N49">
         <v>69</v>
@@ -24088,25 +24094,25 @@
         <v>2006</v>
       </c>
       <c r="R49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="S49">
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="U49" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="V49" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W49" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X49" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Y49">
         <v>0</v>
@@ -24136,16 +24142,16 @@
         <v>470</v>
       </c>
       <c r="AH49" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI49" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ49" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK49" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="50" spans="1:37">
@@ -24167,26 +24173,26 @@
       <c r="F50" t="s">
         <v>278</v>
       </c>
-      <c r="G50">
-        <v>2010</v>
+      <c r="G50" t="s">
+        <v>297</v>
       </c>
       <c r="H50" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I50" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J50" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K50" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L50" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M50" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N50">
         <v>89</v>
@@ -24201,19 +24207,19 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="U50" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="V50" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W50" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X50" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y50">
         <v>0</v>
@@ -24243,16 +24249,16 @@
         <v>157</v>
       </c>
       <c r="AH50" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI50" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ50" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK50" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="51" spans="1:37">
@@ -24274,26 +24280,26 @@
       <c r="F51" t="s">
         <v>279</v>
       </c>
-      <c r="G51">
-        <v>2010</v>
+      <c r="G51" t="s">
+        <v>297</v>
       </c>
       <c r="H51" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I51" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J51" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K51" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L51" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M51" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N51">
         <v>20</v>
@@ -24305,25 +24311,25 @@
         <v>2008</v>
       </c>
       <c r="R51" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="S51">
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="U51" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="V51" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W51" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X51" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="Y51">
         <v>0</v>
@@ -24353,16 +24359,16 @@
         <v>138</v>
       </c>
       <c r="AH51" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI51" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ51" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK51" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="52" spans="1:37">
@@ -24384,26 +24390,26 @@
       <c r="F52" t="s">
         <v>279</v>
       </c>
-      <c r="G52">
-        <v>2010</v>
+      <c r="G52" t="s">
+        <v>297</v>
       </c>
       <c r="H52" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I52" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J52" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K52" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L52" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M52" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N52">
         <v>73</v>
@@ -24418,19 +24424,19 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="U52" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="V52" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W52" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X52" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y52">
         <v>0</v>
@@ -24460,16 +24466,16 @@
         <v>161</v>
       </c>
       <c r="AH52" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI52" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ52" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK52" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="53" spans="1:37">
@@ -24491,26 +24497,26 @@
       <c r="F53" t="s">
         <v>280</v>
       </c>
-      <c r="G53">
-        <v>2010</v>
+      <c r="G53" t="s">
+        <v>297</v>
       </c>
       <c r="H53" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I53" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J53" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K53" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L53" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M53" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -24525,19 +24531,19 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U53" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="V53" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W53" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X53" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="Y53">
         <v>0</v>
@@ -24567,16 +24573,16 @@
         <v>186</v>
       </c>
       <c r="AH53" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI53" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ53" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK53" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="54" spans="1:37">
@@ -24598,26 +24604,26 @@
       <c r="F54" t="s">
         <v>281</v>
       </c>
-      <c r="G54">
-        <v>2010</v>
+      <c r="G54" t="s">
+        <v>297</v>
       </c>
       <c r="H54" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I54" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J54" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K54" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L54" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M54" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N54">
         <v>70</v>
@@ -24629,25 +24635,25 @@
         <v>2008</v>
       </c>
       <c r="R54" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="S54">
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="U54" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="V54" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W54" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X54" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="Y54">
         <v>0</v>
@@ -24677,16 +24683,16 @@
         <v>277</v>
       </c>
       <c r="AH54" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI54" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ54" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK54" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="55" spans="1:37">
@@ -24708,26 +24714,26 @@
       <c r="F55" t="s">
         <v>282</v>
       </c>
-      <c r="G55">
-        <v>2010</v>
+      <c r="G55" t="s">
+        <v>297</v>
       </c>
       <c r="H55" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I55" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J55" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K55" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L55" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M55" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N55">
         <v>68</v>
@@ -24742,19 +24748,19 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="U55" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="V55" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W55" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X55" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="Y55">
         <v>0</v>
@@ -24784,16 +24790,16 @@
         <v>243</v>
       </c>
       <c r="AH55" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI55" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ55" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK55" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="56" spans="1:37">
@@ -24815,26 +24821,26 @@
       <c r="F56" t="s">
         <v>283</v>
       </c>
-      <c r="G56">
-        <v>2010</v>
+      <c r="G56" t="s">
+        <v>297</v>
       </c>
       <c r="H56" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I56" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J56" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K56" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L56" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M56" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N56">
         <v>124</v>
@@ -24849,19 +24855,19 @@
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="U56" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="V56" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W56" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X56" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Y56">
         <v>0</v>
@@ -24891,16 +24897,16 @@
         <v>158</v>
       </c>
       <c r="AH56" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI56" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ56" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK56" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="57" spans="1:37">
@@ -24922,26 +24928,26 @@
       <c r="F57" t="s">
         <v>284</v>
       </c>
-      <c r="G57">
-        <v>2010</v>
+      <c r="G57" t="s">
+        <v>297</v>
       </c>
       <c r="H57" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J57" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K57" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L57" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M57" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N57">
         <v>110</v>
@@ -24956,19 +24962,19 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="U57" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="V57" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W57" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X57" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y57">
         <v>0</v>
@@ -24998,16 +25004,16 @@
         <v>171</v>
       </c>
       <c r="AH57" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI57" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ57" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK57" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="58" spans="1:37">
@@ -25029,26 +25035,26 @@
       <c r="F58" t="s">
         <v>285</v>
       </c>
-      <c r="G58">
-        <v>2010</v>
+      <c r="G58" t="s">
+        <v>297</v>
       </c>
       <c r="H58" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I58" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J58" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K58" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L58" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M58" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N58">
         <v>124</v>
@@ -25060,25 +25066,25 @@
         <v>2007</v>
       </c>
       <c r="R58" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="S58">
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="U58" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="V58" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W58" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X58" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="Y58">
         <v>0</v>
@@ -25108,16 +25114,16 @@
         <v>347</v>
       </c>
       <c r="AH58" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI58" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ58" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK58" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="59" spans="1:37">
@@ -25139,26 +25145,26 @@
       <c r="F59" t="s">
         <v>286</v>
       </c>
-      <c r="G59">
-        <v>2010</v>
+      <c r="G59" t="s">
+        <v>297</v>
       </c>
       <c r="H59" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I59" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J59" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K59" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L59" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M59" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N59">
         <v>126</v>
@@ -25170,25 +25176,25 @@
         <v>2007</v>
       </c>
       <c r="R59" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="S59">
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="U59" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="V59" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W59" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X59" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Y59">
         <v>0</v>
@@ -25218,16 +25224,16 @@
         <v>123</v>
       </c>
       <c r="AH59" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI59" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ59" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK59" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="60" spans="1:37">
@@ -25249,26 +25255,26 @@
       <c r="F60" t="s">
         <v>287</v>
       </c>
-      <c r="G60">
-        <v>2010</v>
+      <c r="G60" t="s">
+        <v>297</v>
       </c>
       <c r="H60" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I60" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J60" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K60" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L60" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M60" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N60">
         <v>118</v>
@@ -25280,25 +25286,25 @@
         <v>2009</v>
       </c>
       <c r="R60" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="S60">
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="U60" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="V60" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W60" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X60" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="Y60">
         <v>0</v>
@@ -25328,16 +25334,16 @@
         <v>198</v>
       </c>
       <c r="AH60" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI60" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ60" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK60" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="61" spans="1:37">
@@ -25359,26 +25365,26 @@
       <c r="F61" t="s">
         <v>288</v>
       </c>
-      <c r="G61">
-        <v>2010</v>
+      <c r="G61" t="s">
+        <v>297</v>
       </c>
       <c r="H61" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I61" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J61" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K61" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L61" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M61" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N61">
         <v>14</v>
@@ -25390,25 +25396,25 @@
         <v>2010</v>
       </c>
       <c r="R61" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S61">
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="U61" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="V61" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W61" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X61" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="Y61">
         <v>0</v>
@@ -25438,16 +25444,16 @@
         <v>221</v>
       </c>
       <c r="AH61" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI61" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ61" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK61" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="62" spans="1:37">
@@ -25469,26 +25475,26 @@
       <c r="F62" t="s">
         <v>289</v>
       </c>
-      <c r="G62">
-        <v>2010</v>
+      <c r="G62" t="s">
+        <v>297</v>
       </c>
       <c r="H62" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I62" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J62" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K62" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L62" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M62" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N62">
         <v>191</v>
@@ -25503,19 +25509,19 @@
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="U62" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="V62" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W62" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X62" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="Y62">
         <v>0</v>
@@ -25545,16 +25551,16 @@
         <v>112</v>
       </c>
       <c r="AH62" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI62" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ62" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK62" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="63" spans="1:37">
@@ -25576,26 +25582,26 @@
       <c r="F63" t="s">
         <v>289</v>
       </c>
-      <c r="G63">
-        <v>2010</v>
+      <c r="G63" t="s">
+        <v>297</v>
       </c>
       <c r="H63" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I63" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J63" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K63" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L63" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M63" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N63">
         <v>123</v>
@@ -25607,25 +25613,25 @@
         <v>2009</v>
       </c>
       <c r="R63" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="S63">
         <v>0</v>
       </c>
       <c r="T63" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="U63" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="V63" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W63" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X63" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Y63">
         <v>0</v>
@@ -25655,16 +25661,16 @@
         <v>262</v>
       </c>
       <c r="AH63" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI63" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ63" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK63" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="64" spans="1:37">
@@ -25686,26 +25692,26 @@
       <c r="F64" t="s">
         <v>290</v>
       </c>
-      <c r="G64">
-        <v>2010</v>
+      <c r="G64" t="s">
+        <v>297</v>
       </c>
       <c r="H64" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I64" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J64" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K64" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L64" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M64" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N64">
         <v>14</v>
@@ -25717,25 +25723,25 @@
         <v>2009</v>
       </c>
       <c r="R64" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="S64">
         <v>0</v>
       </c>
       <c r="T64" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="U64" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="V64" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W64" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X64" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="Y64">
         <v>0</v>
@@ -25765,16 +25771,16 @@
         <v>163</v>
       </c>
       <c r="AH64" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI64" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ64" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK64" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="65" spans="1:37">
@@ -25796,26 +25802,26 @@
       <c r="F65" t="s">
         <v>291</v>
       </c>
-      <c r="G65">
-        <v>2010</v>
+      <c r="G65" t="s">
+        <v>297</v>
       </c>
       <c r="H65" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I65" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J65" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K65" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L65" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M65" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N65">
         <v>46</v>
@@ -25830,19 +25836,19 @@
         <v>0</v>
       </c>
       <c r="T65" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="U65" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="V65" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W65" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X65" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="Y65">
         <v>0</v>
@@ -25872,16 +25878,16 @@
         <v>151</v>
       </c>
       <c r="AH65" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI65" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ65" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK65" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66" spans="1:37">
@@ -25903,26 +25909,26 @@
       <c r="F66" t="s">
         <v>292</v>
       </c>
-      <c r="G66">
-        <v>2010</v>
+      <c r="G66" t="s">
+        <v>297</v>
       </c>
       <c r="H66" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I66" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J66" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K66" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L66" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M66" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N66">
         <v>149</v>
@@ -25934,25 +25940,25 @@
         <v>2007</v>
       </c>
       <c r="R66" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="S66">
         <v>0</v>
       </c>
       <c r="T66" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="U66" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="V66" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W66" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X66" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="Y66">
         <v>0</v>
@@ -25982,16 +25988,16 @@
         <v>255</v>
       </c>
       <c r="AH66" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI66" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ66" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK66" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="67" spans="1:37">
@@ -26013,26 +26019,26 @@
       <c r="F67" t="s">
         <v>293</v>
       </c>
-      <c r="G67">
-        <v>2010</v>
+      <c r="G67" t="s">
+        <v>297</v>
       </c>
       <c r="H67" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I67" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J67" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K67" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L67" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M67" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N67">
         <v>48</v>
@@ -26044,25 +26050,25 @@
         <v>2009</v>
       </c>
       <c r="R67" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="S67">
         <v>0</v>
       </c>
       <c r="T67" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="U67" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="V67" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W67" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X67" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Y67">
         <v>0</v>
@@ -26092,16 +26098,16 @@
         <v>236</v>
       </c>
       <c r="AH67" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI67" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ67" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK67" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="68" spans="1:37">
@@ -26123,26 +26129,26 @@
       <c r="F68" t="s">
         <v>294</v>
       </c>
-      <c r="G68">
-        <v>2010</v>
+      <c r="G68" t="s">
+        <v>297</v>
       </c>
       <c r="H68" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I68" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J68" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K68" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L68" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M68" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N68">
         <v>283</v>
@@ -26157,19 +26163,19 @@
         <v>0</v>
       </c>
       <c r="T68" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="U68" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="V68" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W68" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X68" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y68">
         <v>0</v>
@@ -26199,16 +26205,16 @@
         <v>111</v>
       </c>
       <c r="AH68" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI68" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ68" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK68" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="69" spans="1:37">
@@ -26230,26 +26236,26 @@
       <c r="F69" t="s">
         <v>294</v>
       </c>
-      <c r="G69">
-        <v>2010</v>
+      <c r="G69" t="s">
+        <v>297</v>
       </c>
       <c r="H69" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I69" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J69" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L69" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M69" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N69">
         <v>80</v>
@@ -26264,19 +26270,19 @@
         <v>0</v>
       </c>
       <c r="T69" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="U69" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="V69" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W69" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X69" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="Y69">
         <v>0</v>
@@ -26306,16 +26312,16 @@
         <v>154</v>
       </c>
       <c r="AH69" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI69" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ69" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK69" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="70" spans="1:37">
@@ -26337,26 +26343,26 @@
       <c r="F70" t="s">
         <v>295</v>
       </c>
-      <c r="G70">
-        <v>2010</v>
+      <c r="G70" t="s">
+        <v>297</v>
       </c>
       <c r="H70" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I70" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J70" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K70" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L70" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M70" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N70">
         <v>110</v>
@@ -26368,25 +26374,25 @@
         <v>2008</v>
       </c>
       <c r="R70" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="S70">
         <v>0</v>
       </c>
       <c r="T70" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="U70" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="V70" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W70" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X70" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Y70">
         <v>0</v>
@@ -26416,16 +26422,16 @@
         <v>40</v>
       </c>
       <c r="AH70" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI70" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ70" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK70" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="71" spans="1:37">
@@ -26447,26 +26453,26 @@
       <c r="F71" t="s">
         <v>295</v>
       </c>
-      <c r="G71">
-        <v>2010</v>
+      <c r="G71" t="s">
+        <v>297</v>
       </c>
       <c r="H71" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I71" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J71" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K71" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L71" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M71" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N71">
         <v>66</v>
@@ -26478,25 +26484,25 @@
         <v>2010</v>
       </c>
       <c r="R71" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="S71">
         <v>0</v>
       </c>
       <c r="T71" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="U71" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="V71" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W71" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X71" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="Y71">
         <v>0</v>
@@ -26526,16 +26532,16 @@
         <v>241</v>
       </c>
       <c r="AH71" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI71" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ71" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK71" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="72" spans="1:37">
@@ -26557,26 +26563,26 @@
       <c r="F72" t="s">
         <v>295</v>
       </c>
-      <c r="G72">
-        <v>2010</v>
+      <c r="G72" t="s">
+        <v>297</v>
       </c>
       <c r="H72" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I72" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J72" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K72" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L72" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M72" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="N72">
         <v>81</v>
@@ -26591,19 +26597,19 @@
         <v>0</v>
       </c>
       <c r="T72" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="U72" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="V72" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="W72" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="X72" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Y72">
         <v>0</v>
@@ -26633,16 +26639,16 @@
         <v>53</v>
       </c>
       <c r="AH72" s="3">
-        <v>45560</v>
+        <v>45754</v>
       </c>
       <c r="AI72" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AJ72" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AK72" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
